--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/WISCONSIN_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/WISCONSIN_2010.xlsx
@@ -1824,7 +1824,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C82">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C146">
@@ -9978,7 +9978,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C535">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="B592" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C592">
@@ -15450,7 +15450,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>Yauhquemecan</t>
+          <t>Yauhquemehcan</t>
         </is>
       </c>
       <c r="C839">
@@ -17574,7 +17574,7 @@
       </c>
       <c r="B957" t="inlineStr">
         <is>
-          <t>Tuxpam</t>
+          <t>Tuxpan</t>
         </is>
       </c>
       <c r="C957">
